--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/tektoniektype/tektoniektype.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/tektoniektype/tektoniektype.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,378 +407,353 @@
         <v>type</v>
       </c>
       <c r="C1" t="str">
+        <v>dc\.identifier</v>
+      </c>
+      <c r="D1" t="str">
+        <v>definition</v>
+      </c>
+      <c r="E1" t="str">
         <v>inScheme</v>
-      </c>
-      <c r="D1" t="str">
-        <v>member</v>
-      </c>
-      <c r="E1" t="str">
-        <v>prefLabel</v>
       </c>
       <c r="F1" t="str">
         <v>notation</v>
       </c>
       <c r="G1" t="str">
+        <v>note</v>
+      </c>
+      <c r="H1" t="str">
+        <v>prefLabel</v>
+      </c>
+      <c r="I1" t="str">
         <v>topConceptOf</v>
       </c>
-      <c r="H1" t="str">
-        <v>dc\.identifier</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/collection/tektoniektype/tektoniektype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/br</v>
       </c>
       <c r="B2" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Collection</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.br</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/0|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/1|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/2|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/3|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/4|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/5|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/6|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/7|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/8|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/9</v>
+        <v>Een herkenbaar doorlopend vlak in het gesteente, waar het gesteente is opgebroken.</v>
       </c>
       <c r="E2" t="str">
-        <v>Collectie van tektoniektype.</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F2" t="str">
-        <v>null</v>
+        <v>BR</v>
       </c>
       <c r="G2" t="str">
-        <v>null</v>
+        <v>Een herkenbaar doorlopend vlak in het gesteente, waar het gesteente is opgebroken.</v>
       </c>
       <c r="H2" t="str">
-        <v>null</v>
+        <v>breukvlak</v>
       </c>
       <c r="I2" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J2" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/0</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/ca</v>
       </c>
       <c r="B3" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C3" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.ca</v>
       </c>
       <c r="D3" t="str">
-        <v>null</v>
+        <v>Spleten in het gesteente (van diverse oorsprong) die opgevuld zijn met calciet.</v>
       </c>
       <c r="E3" t="str">
-        <v>onbepaald</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>CA</v>
       </c>
       <c r="G3" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Spleten in het gesteente (van diverse oorsprong) die opgevuld zijn met calciet.</v>
       </c>
       <c r="H3" t="str">
-        <v>null</v>
+        <v>calcietgevulde spleten</v>
       </c>
       <c r="I3" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J3" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/1</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/di</v>
       </c>
       <c r="B4" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.di</v>
       </c>
       <c r="D4" t="str">
-        <v>null</v>
+        <v>Een spleet of breuk in het gesteente waarlangs geen of nauwelijkse beweging is opgetreden maar waar het gesteente uit elkaar is bewogen door extensieve spanning.</v>
       </c>
       <c r="E4" t="str">
-        <v>glijvlak / verschuivingsvlak</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>DI</v>
       </c>
       <c r="G4" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Een spleet of breuk in het gesteente waarlangs geen of nauwelijkse beweging is opgetreden maar waar het gesteente uit elkaar is bewogen door extensieve spanning.</v>
       </c>
       <c r="H4" t="str">
-        <v>null</v>
+        <v>diaklaas</v>
       </c>
       <c r="I4" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J4" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/2</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/gl</v>
       </c>
       <c r="B5" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.gl</v>
       </c>
       <c r="D5" t="str">
-        <v>null</v>
+        <v>Een herkenbaar doorlopend vlak in het gesteente, waarlangs een verschuiving is opgetreden.</v>
       </c>
       <c r="E5" t="str">
-        <v>diaklaas</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F5" t="str">
-        <v>2</v>
+        <v>GL</v>
       </c>
       <c r="G5" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Een herkenbaar doorlopend vlak in het gesteente, waarlangs een verschuiving is opgetreden.</v>
       </c>
       <c r="H5" t="str">
-        <v>null</v>
+        <v>glijvlak / verschuivingsvlak</v>
       </c>
       <c r="I5" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J5" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/3</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/on</v>
       </c>
       <c r="B6" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C6" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.on</v>
       </c>
       <c r="D6" t="str">
-        <v>null</v>
+        <v>Het tektoniektype werd niet bepaald.</v>
       </c>
       <c r="E6" t="str">
-        <v>breukvlak</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F6" t="str">
-        <v>3</v>
+        <v>ON</v>
       </c>
       <c r="G6" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Het tektoniektype werd niet bepaald.</v>
       </c>
       <c r="H6" t="str">
-        <v>null</v>
+        <v>onbepaald</v>
       </c>
       <c r="I6" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J6" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/4</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/pl</v>
       </c>
       <c r="B7" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.pl</v>
       </c>
       <c r="D7" t="str">
-        <v>null</v>
+        <v>Een plooi in het gesteente die gevormd is aan het contact tussen de gesteentelagen en een verschuivingsvlak, door weerstand bij de beweging van gesteenten langsheen dit vlak.</v>
       </c>
       <c r="E7" t="str">
-        <v>diaklaasafstand</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F7" t="str">
-        <v>4</v>
+        <v>PL</v>
       </c>
       <c r="G7" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Een plooi in het gesteente die gevormd is aan het contact tussen de gesteentelagen en een verschuivingsvlak, door weerstand bij de beweging van gesteenten langsheen dit vlak.</v>
       </c>
       <c r="H7" t="str">
-        <v>null</v>
+        <v>plooiing (crochon)</v>
       </c>
       <c r="I7" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J7" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/5</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/sp</v>
       </c>
       <c r="B8" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.sp</v>
       </c>
       <c r="D8" t="str">
-        <v>null</v>
+        <v>Een vlak in het gesteente gevormd door de oplijning van mineralen loodrecht op de overheersende drukrichting, bv. door diepe begraving (verticale druk) of gebergtevorming (laterale druk).</v>
       </c>
       <c r="E8" t="str">
-        <v>plooiing (crochon)</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F8" t="str">
-        <v>5</v>
+        <v>SP</v>
       </c>
       <c r="G8" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Een vlak in het gesteente gevormd door de oplijning van mineralen loodrecht op de overheersende drukrichting, bv. door diepe begraving (verticale druk) of gebergtevorming (laterale druk).</v>
       </c>
       <c r="H8" t="str">
-        <v>null</v>
+        <v>splijtingsvlak</v>
       </c>
       <c r="I8" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J8" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/6</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/st</v>
       </c>
       <c r="B9" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.st</v>
       </c>
       <c r="D9" t="str">
-        <v>null</v>
+        <v>Een onregelmatig vlak in het gesteente gevormd door de oplossing van materiaal loodrecht op de overheersende drukrichting en het achterblijven van onoplosbare mineralen. Vaak gevormd in (goed oplosbare) kalksteen.</v>
       </c>
       <c r="E9" t="str">
-        <v>splijtingsvlak</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="F9" t="str">
-        <v>6</v>
+        <v>ST</v>
       </c>
       <c r="G9" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>Een onregelmatig vlak in het gesteente gevormd door de oplossing van materiaal loodrecht op de overheersende drukrichting en het achterblijven van onoplosbare mineralen. Vaak gevormd in (goed oplosbare) kalksteen.</v>
       </c>
       <c r="H9" t="str">
-        <v>null</v>
+        <v>stylolieten</v>
       </c>
       <c r="I9" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/7</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/zv</v>
       </c>
       <c r="B10" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.tektoniektype.zv</v>
       </c>
       <c r="D10" t="str">
-        <v>null</v>
+        <v>Fijne voegen in het gesteente opgevuld met zwart materiaal.</v>
       </c>
       <c r="E10" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="F10" t="str">
+        <v>ZV</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Fijne voegen in het gesteente opgevuld met zwart materiaal.</v>
+      </c>
+      <c r="H10" t="str">
         <v>fijne zwarte voegen</v>
       </c>
-      <c r="F10" t="str">
-        <v>7</v>
-      </c>
-      <c r="G10" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
-      </c>
-      <c r="H10" t="str">
-        <v>null</v>
-      </c>
       <c r="I10" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+      </c>
+      <c r="J10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/8</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
       </c>
       <c r="B11" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C11" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.conceptscheme.tektoniektype</v>
       </c>
       <c r="D11" t="str">
         <v>null</v>
       </c>
       <c r="E11" t="str">
-        <v>calcietgevulde spleten</v>
+        <v>null</v>
       </c>
       <c r="F11" t="str">
-        <v>8</v>
+        <v>null</v>
       </c>
       <c r="G11" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
+        <v>null</v>
       </c>
       <c r="H11" t="str">
-        <v>null</v>
+        <v>lijst van tektoniektypes</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/9</v>
-      </c>
-      <c r="B12" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
-      </c>
-      <c r="C12" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
-      </c>
-      <c r="D12" t="str">
-        <v>null</v>
-      </c>
-      <c r="E12" t="str">
-        <v>stylolieten</v>
-      </c>
-      <c r="F12" t="str">
-        <v>9</v>
-      </c>
-      <c r="G12" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
-      </c>
-      <c r="H12" t="str">
-        <v>null</v>
-      </c>
-      <c r="I12" t="str">
-        <v>null</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/tektoniektype</v>
-      </c>
-      <c r="B13" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C13" t="str">
-        <v>null</v>
-      </c>
-      <c r="D13" t="str">
-        <v>null</v>
-      </c>
-      <c r="E13" t="str">
-        <v>lijst van tektoniektypes</v>
-      </c>
-      <c r="F13" t="str">
-        <v>null</v>
-      </c>
-      <c r="G13" t="str">
-        <v>null</v>
-      </c>
-      <c r="H13" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.conceptscheme.tektoniektype</v>
-      </c>
-      <c r="I13" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/0|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/1|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/2|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/3|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/4|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/5|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/6|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/7|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/8|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/9</v>
+      <c r="J11" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/br|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/ca|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/di|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/gl|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/on|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/pl|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/sp|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/st|https://data.bodemenondergrond.vlaanderen.be/id/concept/tektoniektype/zv</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J11"/>
   </ignoredErrors>
 </worksheet>
 </file>